--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1406,6 +1406,111 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128457794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86730</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>448</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mjölspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius flavovirens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källstädhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>710652</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6387806</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1411,7 +1411,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86730</v>
+        <v>86822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,12 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710499.693744536</v>
+        <v>710500</v>
       </c>
       <c r="R4" t="n">
-        <v>6387842.306027657</v>
+        <v>6387842</v>
       </c>
       <c r="S4" t="n">
         <v>71</v>
@@ -982,19 +977,9 @@
           <t>1985-11-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1985-11-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,12 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>100520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710499.693744536</v>
+        <v>710500</v>
       </c>
       <c r="R5" t="n">
-        <v>6387842.306027657</v>
+        <v>6387842</v>
       </c>
       <c r="S5" t="n">
         <v>71</v>
@@ -1103,19 +1083,9 @@
           <t>1999-07-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1159,12 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>710499.693744536</v>
+        <v>710500</v>
       </c>
       <c r="R6" t="n">
-        <v>6387842.306027657</v>
+        <v>6387842</v>
       </c>
       <c r="S6" t="n">
         <v>71</v>
@@ -1229,19 +1194,9 @@
           <t>1999-07-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,12 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>710499.693744536</v>
+        <v>710500</v>
       </c>
       <c r="R7" t="n">
-        <v>6387842.306027657</v>
+        <v>6387842</v>
       </c>
       <c r="S7" t="n">
         <v>71</v>
@@ -1355,19 +1305,9 @@
           <t>1999-07-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105704</v>
+        <v>105713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102816</v>
+        <v>102824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86822</v>
+        <v>86832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105713</v>
+        <v>105725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102824</v>
+        <v>102834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86832</v>
+        <v>86834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105725</v>
+        <v>105734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102834</v>
+        <v>102840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105734</v>
+        <v>105739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102840</v>
+        <v>102841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105739</v>
+        <v>105767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102841</v>
+        <v>102868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86834</v>
+        <v>86861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105767</v>
+        <v>105773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102868</v>
+        <v>102874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105773</v>
+        <v>105780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102874</v>
+        <v>102881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86861</v>
+        <v>86866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105780</v>
+        <v>105784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102881</v>
+        <v>102885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86866</v>
+        <v>86870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102885</v>
+        <v>102892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128457794</v>
       </c>
       <c r="B8" t="n">
-        <v>86870</v>
+        <v>86875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105794</v>
+        <v>105799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>105100400</v>
       </c>
       <c r="B4" t="n">
-        <v>105799</v>
+        <v>105807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>105100403</v>
       </c>
       <c r="B5" t="n">
-        <v>102900</v>
+        <v>102908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>105100405</v>
       </c>
       <c r="B6" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>105100397</v>
       </c>
       <c r="B7" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,6 +1451,410 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129738765</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4037</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bolmörtsskivling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Entoloma sinuatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bull.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källstädhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>710660</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6387886</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129738748</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86864</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Källstädhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>710637</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6387834</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129738761</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86864</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Källstädhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>710659</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6387814</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129738754</v>
+      </c>
+      <c r="B12" t="n">
+        <v>88774</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Källstädhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>710647</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6387835</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90005</v>
+        <v>90006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86864</v>
+        <v>86865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86864</v>
+        <v>86865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88774</v>
+        <v>88775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90006</v>
+        <v>90011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86865</v>
+        <v>86870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86865</v>
+        <v>86870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88775</v>
+        <v>88780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90011</v>
+        <v>90015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88780</v>
+        <v>88784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90015</v>
+        <v>90017</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86874</v>
+        <v>86876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86874</v>
+        <v>86876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88784</v>
+        <v>88786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90017</v>
+        <v>90020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88786</v>
+        <v>88789</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90020</v>
+        <v>90023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88789</v>
+        <v>88792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90023</v>
+        <v>90024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86882</v>
+        <v>86883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86882</v>
+        <v>86883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88792</v>
+        <v>88793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>129738765</v>
       </c>
       <c r="B9" t="n">
-        <v>90024</v>
+        <v>90041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129738748</v>
       </c>
       <c r="B10" t="n">
-        <v>86883</v>
+        <v>86900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129738761</v>
       </c>
       <c r="B11" t="n">
-        <v>86883</v>
+        <v>86900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129738754</v>
       </c>
       <c r="B12" t="n">
-        <v>88793</v>
+        <v>88810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7210961</v>
+        <v>128457794</v>
       </c>
       <c r="B2" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>655</v>
+        <v>448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Mjölspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Cortinarius flavovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekeby Röstäde, Gtl</t>
+          <t>Källstädhagen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710650.1826400044</v>
+        <v>710652</v>
       </c>
       <c r="R2" t="n">
-        <v>6387794.266568324</v>
+        <v>6387806</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-10-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,60 +761,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fårbete</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elsa Bohus Jensen</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Bohus Jensen</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7210975</v>
+        <v>7210961</v>
       </c>
       <c r="B3" t="n">
-        <v>87252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1054</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stinkbrosking</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnopus foetidus</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sowerby:Fr.) P.M.Kirk</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710650.1826400044</v>
+        <v>710650</v>
       </c>
       <c r="R3" t="n">
-        <v>6387794.266568324</v>
+        <v>6387794</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,21 +848,11 @@
           <t>1997-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-10-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +864,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>igenväxt blandskog</t>
+          <t>fårbete</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105100400</v>
+        <v>7210975</v>
       </c>
       <c r="B4" t="n">
-        <v>105807</v>
+        <v>89345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>1054</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Stinkbrosking</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Gymnopus foetidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Sowerby) P.M.Kirk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
+          <t>Ekeby Röstäde, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710500</v>
+        <v>710650</v>
       </c>
       <c r="R4" t="n">
-        <v>6387842</v>
+        <v>6387794</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1985-11-22</t>
+          <t>1997-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-11-22</t>
+          <t>1997-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,70 +966,69 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Järnåldershusgrundområde i lövskog</t>
+          <t>igenväxt blandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Elsa Bohus Jensen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Elsa Bohus Jensen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105100403</v>
+        <v>129738748</v>
       </c>
       <c r="B5" t="n">
-        <v>102908</v>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223248</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lundalm</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
+          <t>Källstädhagen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710500</v>
+        <v>710637</v>
       </c>
       <c r="R5" t="n">
-        <v>6387842</v>
+        <v>6387834</v>
       </c>
       <c r="S5" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,17 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ungefärlig koordinat</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,75 +1066,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105100405</v>
+        <v>129738761</v>
       </c>
       <c r="B6" t="n">
-        <v>106284</v>
+        <v>87170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
+          <t>Källstädhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>710500</v>
+        <v>710659</v>
       </c>
       <c r="R6" t="n">
-        <v>6387842</v>
+        <v>6387814</v>
       </c>
       <c r="S6" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ungefärlig koordinat</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,37 +1167,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105100397</v>
+        <v>129738765</v>
       </c>
       <c r="B7" t="n">
-        <v>103181</v>
+        <v>90312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1197,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222002</v>
+        <v>4037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Bolmörtsskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Entoloma sinuatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bull.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
+          <t>Källstädhagen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>710500</v>
+        <v>710660</v>
       </c>
       <c r="R7" t="n">
-        <v>6387842</v>
+        <v>6387886</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,17 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-07-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ungefärlig koordinat</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,66 +1268,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128457794</v>
+        <v>129738754</v>
       </c>
       <c r="B8" t="n">
-        <v>86877</v>
+        <v>89085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>448</v>
+        <v>4379</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjölspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius flavovirens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>710652</v>
+        <v>710647</v>
       </c>
       <c r="R8" t="n">
-        <v>6387806</v>
+        <v>6387835</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,12 +1355,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,51 +1388,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129738765</v>
+        <v>105100405</v>
       </c>
       <c r="B9" t="n">
-        <v>90056</v>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4037</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bolmörtsskivling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Entoloma sinuatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bull.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källstädhagen, Gtl</t>
+          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>710660</v>
+        <v>710500</v>
       </c>
       <c r="R9" t="n">
-        <v>6387886</v>
+        <v>6387842</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,12 +1453,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ungefärlig koordinat</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,29 +1472,37 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129738748</v>
+        <v>105100400</v>
       </c>
       <c r="B10" t="n">
-        <v>86915</v>
+        <v>106329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,40 +1510,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3712</v>
+        <v>221423</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källstädhagen, Gtl</t>
+          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>710637</v>
+        <v>710500</v>
       </c>
       <c r="R10" t="n">
-        <v>6387834</v>
+        <v>6387842</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,12 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1985-11-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1985-11-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,29 +1578,37 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Järnåldershusgrundområde i lövskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129738761</v>
+        <v>105100397</v>
       </c>
       <c r="B11" t="n">
-        <v>86915</v>
+        <v>103683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,40 +1616,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>222002</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källstädhagen, Gtl</t>
+          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>710659</v>
+        <v>710500</v>
       </c>
       <c r="R11" t="n">
-        <v>6387814</v>
+        <v>6387842</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1670,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ungefärlig koordinat</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,70 +1689,75 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129738754</v>
+        <v>105100403</v>
       </c>
       <c r="B12" t="n">
-        <v>88825</v>
+        <v>103408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4379</v>
+        <v>223248</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Lundalm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källstädhagen, Gtl</t>
+          <t>Stora Röstäde 1:53 1100 m OSO, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>710647</v>
+        <v>710500</v>
       </c>
       <c r="R12" t="n">
-        <v>6387835</v>
+        <v>6387842</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,12 +1781,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>1999-07-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ungefärlig koordinat</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,22 +1800,30 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Järnåldershusgrund i betad lövskog, nära. Silikatsten i huset.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45248-2024 artfynd.xlsx
+++ b/artfynd/A 45248-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457794</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7210961</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7210975</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129738761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129738748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129738765</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129738754</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105100405</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105100400</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105100397</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,8 +1879,26 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105100403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>